--- a/data/excel/equipments.xlsx
+++ b/data/excel/equipments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SunnydayBot\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8794A168-B050-4637-B9E4-4946652FED93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA0D9E3-8945-45A0-A861-9319A5E96E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -323,6 +323,21 @@
   </si>
   <si>
     <t>wraith_of_gold</t>
+  </si>
+  <si>
+    <t>buildup</t>
+  </si>
+  <si>
+    <t>frost_blade</t>
+  </si>
+  <si>
+    <t>Frost Blade</t>
+  </si>
+  <si>
+    <t>magic</t>
+  </si>
+  <si>
+    <t>frost</t>
   </si>
 </sst>
 </file>
@@ -662,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
@@ -672,7 +687,7 @@
     <col min="10" max="10" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -707,10 +722,13 @@
         <v>9</v>
       </c>
       <c r="L1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -741,11 +759,11 @@
       <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -776,11 +794,11 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -814,11 +832,14 @@
       <c r="K4" t="s">
         <v>25</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4">
+        <v>70</v>
+      </c>
+      <c r="M4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -849,11 +870,11 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -884,11 +905,11 @@
       <c r="J6" t="s">
         <v>15</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -919,8 +940,46 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
